--- a/main/ig/StructureDefinition-eclaire-researchstudy.xlsx
+++ b/main/ig/StructureDefinition-eclaire-researchstudy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-25T15:44:45+00:00</t>
+    <t>2025-11-27T10:20:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -385,7 +385,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -653,8 +653,8 @@
     <t>Allows identification of the research study as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:use}
-</t>
+    <t>value:use}
+value:system}</t>
   </si>
   <si>
     <t>Slicing pour les différents identifiants de l'essai clinique</t>
@@ -779,7 +779,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -955,7 +955,7 @@
     <t>ResearchStudy.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1038,7 +1038,7 @@
     <t>ResearchStudy.protocol</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(PlanDefinition)
+    <t xml:space="preserve">Reference(PlanDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1067,7 +1067,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ResearchStudy)
+    <t xml:space="preserve">Reference(ResearchStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -1125,7 +1125,7 @@
     <t>Codes for the main intent of the study.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-prim-purp-type</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-prim-purp-type|4.0.1</t>
   </si>
   <si>
     <t>StudyProtocolVersion.primaryPurposeTypeCode</t>
@@ -1209,7 +1209,7 @@
     <t>Identification of the condition or diagnosis.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>Slicing pour apporter des précisions sur le sujet / Health Condition(s) or Problem(s) Studied. Dans le CTIS, il y a un champ texte ouvert (obligatoire) pour indiquer la pathologie et éventuellement des précisons. Un code MedDRA peut-être ajouté mais il est optionnel.
@@ -1655,7 +1655,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>StudyProtocolVersion.participatingLocationCode</t>
@@ -1785,7 +1785,7 @@
     <t>ResearchStudy.principalInvestigator</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1838,7 +1838,7 @@
     <t>Codes for why the study ended prematurely.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-reason-stopped</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-reason-stopped|4.0.1</t>
   </si>
   <si>
     <t>StudyOverallStatus.studyStoppedReasonCode</t>
@@ -2020,7 +2020,7 @@
     <t>Codes for the kind of study objective.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/research-study-objective-type</t>
+    <t>http://hl7.org/fhir/ValueSet/research-study-objective-type|4.0.1</t>
   </si>
   <si>
     <t>StudyObjective.typeCode</t>
@@ -3442,7 +3442,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>147</v>
       </c>
@@ -3559,7 +3559,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>152</v>
       </c>
@@ -3676,7 +3676,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>157</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>162</v>
       </c>
@@ -3910,7 +3910,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>167</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>172</v>
       </c>
@@ -4144,7 +4144,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>177</v>
       </c>
@@ -4261,7 +4261,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>182</v>
       </c>
@@ -4378,7 +4378,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>187</v>
       </c>
@@ -4731,7 +4731,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>209</v>
       </c>
@@ -6258,7 +6258,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>308</v>
       </c>
@@ -7317,7 +7317,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>320</v>
       </c>
@@ -7670,7 +7670,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>342</v>
       </c>
@@ -7787,7 +7787,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>350</v>
       </c>
@@ -7904,7 +7904,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>359</v>
       </c>
@@ -8019,7 +8019,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>365</v>
       </c>
@@ -8251,7 +8251,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>379</v>
       </c>
@@ -8368,7 +8368,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>387</v>
       </c>
@@ -9782,7 +9782,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>462</v>
       </c>
@@ -10371,7 +10371,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
         <v>470</v>
       </c>
@@ -10718,7 +10718,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>478</v>
       </c>
@@ -10835,7 +10835,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>483</v>
       </c>
@@ -10952,7 +10952,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
         <v>488</v>
       </c>
@@ -11069,7 +11069,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
         <v>493</v>
       </c>
@@ -11418,7 +11418,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>511</v>
       </c>
@@ -11652,7 +11652,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
         <v>524</v>
       </c>
@@ -11769,7 +11769,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>530</v>
       </c>
@@ -11886,7 +11886,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
         <v>537</v>
       </c>
@@ -12469,7 +12469,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>560</v>
       </c>
@@ -12822,7 +12822,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
         <v>576</v>
       </c>
@@ -13520,7 +13520,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
         <v>606</v>
       </c>
@@ -14809,12 +14809,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO106">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/main/ig/StructureDefinition-eclaire-researchstudy.xlsx
+++ b/main/ig/StructureDefinition-eclaire-researchstudy.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-27T10:20:46+00:00</t>
+    <t>2025-11-27T15:06:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
